--- a/data/trans_dic/IQ26A_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ26A_R2-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,28%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9,8%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13,88%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>8,19%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16,3%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31,77%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 12,55</t>
+          <t>4,93; 12,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,59</t>
+          <t>5,82; 15,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,4; 21,54</t>
+          <t>7,2; 15,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,87; 48,5</t>
+          <t>4,94; 29,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,15; 12,61</t>
+          <t>5,19; 13,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 14,25</t>
+          <t>2,94; 9,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,22; 16,1</t>
+          <t>11,32; 22,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 29,06</t>
+          <t>20,15; 45,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 11,08</t>
+          <t>5,95; 11,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 10,75</t>
+          <t>5,65; 10,96</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,62</t>
+          <t>10,52; 17,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,87; 30,8</t>
+          <t>14,33; 32,55</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,77%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>17,09%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>12,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,77%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,21; 21,85</t>
+          <t>9,24; 16,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 15,97</t>
+          <t>6,21; 12,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,48; 14,43</t>
+          <t>7,38; 14,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,18; 32,26</t>
+          <t>13,06; 32,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 16,23</t>
+          <t>12,96; 21,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 12,66</t>
+          <t>8,97; 16,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,97; 14,65</t>
+          <t>7,31; 14,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,12; 30,17</t>
+          <t>9,99; 32,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,09; 17,67</t>
+          <t>12,18; 17,72</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 12,71</t>
+          <t>8,21; 13,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,49; 13,18</t>
+          <t>8,45; 13,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 27,73</t>
+          <t>14,02; 29,27</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,19%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>21,42%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>10,38%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,22%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>19,36%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,19%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>23,52%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 14,98</t>
+          <t>8,61; 17,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 15,78</t>
+          <t>7,72; 15,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,78; 24,77</t>
+          <t>11,62; 21,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12,32; 37,91</t>
+          <t>11,69; 36,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 16,74</t>
+          <t>6,84; 15,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 15,56</t>
+          <t>7,68; 16,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 20,72</t>
+          <t>14,43; 24,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 31,33</t>
+          <t>14,74; 42,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,81; 14,51</t>
+          <t>8,5; 14,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 14,3</t>
+          <t>8,24; 14,17</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,16; 21,08</t>
+          <t>14,28; 21,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,84; 30,46</t>
+          <t>15,41; 34,63</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16,42%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,73%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,94%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23,6%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 20,36</t>
+          <t>10,95; 19,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 16,07</t>
+          <t>10,42; 18,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 18,85</t>
+          <t>15,71; 25,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,32; 38,88</t>
+          <t>7,88; 29,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 18,78</t>
+          <t>12,02; 20,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 18,62</t>
+          <t>8,41; 16,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,64; 25,51</t>
+          <t>10,05; 18,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,77; 30,59</t>
+          <t>10,64; 31,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 18,63</t>
+          <t>12,43; 18,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,98</t>
+          <t>9,8; 15,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 20,36</t>
+          <t>14,0; 20,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 28,96</t>
+          <t>11,65; 26,76</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>12,11%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>13,63%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>14,57%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,38; 15,74</t>
+          <t>10,22; 14,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 12,63</t>
+          <t>9,15; 13,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,86</t>
+          <t>12,32; 16,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,56; 31,16</t>
+          <t>13,88; 23,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,29</t>
+          <t>11,84; 15,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 13,11</t>
+          <t>8,67; 12,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,47; 16,98</t>
+          <t>12,71; 16,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>13,39; 23,93</t>
+          <t>18,13; 30,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,49; 14,39</t>
+          <t>11,28; 14,33</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 12,22</t>
+          <t>9,43; 12,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13,05; 16,08</t>
+          <t>13,03; 16,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,0; 25,21</t>
+          <t>17,03; 25,11</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12308</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>14369</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16544</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4452</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>10922</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>7773</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>21383</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>8379</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12308</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14369</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>16544</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>12951</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6353; 16728</t>
+          <t>7332; 18553</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4083; 13227</t>
+          <t>8535; 22035</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14947; 28248</t>
+          <t>10608; 23264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5240; 12790</t>
+          <t>1584; 9328</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7654; 18740</t>
+          <t>6915; 17554</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8991; 20910</t>
+          <t>4053; 13780</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10633; 23722</t>
+          <t>14848; 29107</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1530; 9914</t>
+          <t>5413; 12323</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16446; 31224</t>
+          <t>16783; 31654</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14885; 30601</t>
+          <t>16075; 31214</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29279; 49078</t>
+          <t>29299; 48325</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>8388; 18631</t>
+          <t>8447; 19187</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26253</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19176</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12454</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>33031</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>24009</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>21384</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7846</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26253</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>19176</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23886</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>7844</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>20491</t>
+          <t>20298</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25545; 42245</t>
+          <t>19425; 34812</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17432; 31732</t>
+          <t>13482; 27152</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15238; 29374</t>
+          <t>16357; 31964</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4002; 12684</t>
+          <t>7680; 18934</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>18967; 34124</t>
+          <t>25046; 41137</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13538; 27493</t>
+          <t>17818; 32794</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17687; 32482</t>
+          <t>14879; 28509</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7575; 18861</t>
+          <t>3932; 12940</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48785; 71305</t>
+          <t>49136; 71517</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33726; 52832</t>
+          <t>34120; 54344</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>36096; 56057</t>
+          <t>35941; 56254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13751; 28241</t>
+          <t>13763; 28727</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,44 +1993,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>17779</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17933</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26017</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8892</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>13759</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>16890</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>29609</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>7290</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>17779</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>17933</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>26017</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>8434</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31538</t>
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>16181</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9081; 19859</t>
+          <t>12553; 25172</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11438; 23747</t>
+          <t>12234; 24530</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22595; 37873</t>
+          <t>19145; 34767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3724; 11457</t>
+          <t>4853; 15037</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12397; 24400</t>
+          <t>9068; 20784</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11830; 24642</t>
+          <t>11549; 24229</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18922; 34153</t>
+          <t>22066; 37213</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4505; 13845</t>
+          <t>4020; 11694</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24523; 40389</t>
+          <t>23673; 40823</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27067; 44154</t>
+          <t>25451; 43764</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44979; 66961</t>
+          <t>45380; 67849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10301; 22664</t>
+          <t>10602; 23823</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29787</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>28631</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>40549</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7489</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>33007</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>23599</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>28432</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10794</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29787</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>28631</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40549</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19332</t>
+          <t>16368</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23884; 41991</t>
+          <t>22606; 39286</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16483; 32331</t>
+          <t>20959; 38066</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20868; 38450</t>
+          <t>31848; 51074</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6090; 17783</t>
+          <t>3594; 13366</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22857; 38783</t>
+          <t>24798; 43148</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20789; 37457</t>
+          <t>16920; 33185</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31715; 51723</t>
+          <t>20492; 37378</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3871; 15244</t>
+          <t>4740; 13835</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>51689; 76892</t>
+          <t>51287; 75307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41354; 64289</t>
+          <t>39440; 63738</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57107; 82809</t>
+          <t>56946; 82493</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12391; 27679</t>
+          <t>10502; 24120</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>104</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>54</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>86126</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>80108</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>106996</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>33286</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>90719</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>72270</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>100807</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34308</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>86126</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80108</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>106996</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34087</t>
+          <t>32512</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>65798</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>75760; 104758</t>
+          <t>72698; 102824</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59395; 86929</t>
+          <t>66216; 94161</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87132; 116586</t>
+          <t>90733; 122750</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26286; 44143</t>
+          <t>24706; 42485</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>72335; 101655</t>
+          <t>78806; 105613</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>67074; 94857</t>
+          <t>59649; 86380</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91825; 125082</t>
+          <t>87884; 117410</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25523; 45615</t>
+          <t>25021; 42385</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158159; 198043</t>
+          <t>155289; 197327</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>133547; 172507</t>
+          <t>133112; 171127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>186417; 229676</t>
+          <t>186116; 232128</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56479; 83764</t>
+          <t>53818; 79361</t>
         </is>
       </c>
     </row>
